--- a/Side Bar Files/GWD Data/PVC With Trench.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench.xlsx
@@ -321,23 +321,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -806,7 +816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{688E0985-18B6-4490-BC76-133047B9B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6062BF2-4BD8-48DD-9C41-C545A333B9A7}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC With Trench.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench.xlsx
@@ -9,13 +9,19 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="34">
   <si>
     <t>PVC Pipe With Trenching</t>
   </si>
@@ -99,6 +105,24 @@
   </si>
   <si>
     <t>PVC Pipe, 10kg/cm2, 63mm Dia.</t>
+  </si>
+  <si>
+    <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 90 mm dia 10 KGF/cm2</t>
+  </si>
+  <si>
+    <t>MR10236</t>
+  </si>
+  <si>
+    <t>PVC Pipe, 10kg/cm2, 90mm Dia</t>
+  </si>
+  <si>
+    <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 90 mm dia 6 KGF/cm2</t>
+  </si>
+  <si>
+    <t>MR10213</t>
+  </si>
+  <si>
+    <t>PVC Pipe, 6kg/cm2, 90mm Dia</t>
   </si>
 </sst>
 </file>
@@ -291,25 +315,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -435,11 +445,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -518,6 +528,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HP Erection and Pullout"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -816,8 +933,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6062BF2-4BD8-48DD-9C41-C545A333B9A7}">
-  <dimension ref="A1:F51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0507F162-605C-461B-9B56-E333CA44BAA6}">
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75">
@@ -896,11 +1013,12 @@
         <v>11.50</v>
       </c>
       <c r="E6" s="11">
-        <v>475</v>
+        <f t="array" ref="E6">IFERROR(INDEX(LMRRates,MATCH(A6,LMRCodes,0),),)</f>
+        <v>284</v>
       </c>
       <c r="F6" s="12">
         <f>D6*E6</f>
-        <v>5462.50</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.75">
@@ -923,7 +1041,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="15">
         <f>F6*0.01</f>
-        <v>54.625</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
@@ -936,7 +1054,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="15">
         <f>SUM(F6:F8)</f>
-        <v>5517.125</v>
+        <v>3298.66</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
@@ -949,7 +1067,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="15">
         <f>F9*0.15</f>
-        <v>827.56875000000002</v>
+        <v>494.79899999999998</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
@@ -962,7 +1080,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="15">
         <f>SUM(F9:F10)</f>
-        <v>6344.6937500000004</v>
+        <v>3793.4589999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
@@ -975,7 +1093,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="15">
         <f>F11</f>
-        <v>6344.6937500000004</v>
+        <v>3793.4589999999998</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75">
@@ -988,7 +1106,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="16">
         <f>ROUND(F12/10,2)</f>
-        <v>634.47</v>
+        <v>379.35</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="12.75">
@@ -1179,7 +1297,7 @@
     <row r="26" spans="1:6" ht="12.75">
       <c r="A26" s="22" t="str">
         <f>CONCATENATE("Say ₹ ",F13," + ",F25," x Cost Index")</f>
-        <v>Say ₹ 634.47 + 128.55 x Cost Index</v>
+        <v>Say ₹ 379.35 + 128.55 x Cost Index</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1253,11 +1371,12 @@
         <v>11.50</v>
       </c>
       <c r="E31" s="27">
-        <v>150</v>
+        <f t="array" ref="E31">IFERROR(INDEX(LMRRates,MATCH(A31,LMRCodes,0),),)</f>
+        <v>95</v>
       </c>
       <c r="F31" s="28">
         <f>D31*E31</f>
-        <v>1725</v>
+        <v>1092.50</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="12.75">
@@ -1280,7 +1399,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="31">
         <f>F31*0.01</f>
-        <v>17.25</v>
+        <v>10.925</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="12.75">
@@ -1293,7 +1412,7 @@
       <c r="E34" s="7"/>
       <c r="F34" s="31">
         <f>SUM(F31:F33)</f>
-        <v>1742.25</v>
+        <v>1103.425</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="12.75">
@@ -1306,7 +1425,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="31">
         <f>F34*0.15</f>
-        <v>261.3375</v>
+        <v>165.51375</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="12.75">
@@ -1319,7 +1438,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="31">
         <f>SUM(F34:F35)</f>
-        <v>2003.5875000000001</v>
+        <v>1268.93875</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="12.75">
@@ -1332,7 +1451,7 @@
       <c r="E37" s="7"/>
       <c r="F37" s="31">
         <f>F36</f>
-        <v>2003.5875000000001</v>
+        <v>1268.93875</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="12.75">
@@ -1345,7 +1464,7 @@
       <c r="E38" s="7"/>
       <c r="F38" s="32">
         <f>ROUND(F37/10,2)</f>
-        <v>200.36</v>
+        <v>126.89</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="12.75">
@@ -1536,7 +1655,7 @@
     <row r="51" spans="1:6" ht="12.75">
       <c r="A51" s="38" t="str">
         <f>CONCATENATE("Say ₹ ",F38," + ",F50," x Cost Index")</f>
-        <v>Say ₹ 200.36 + 128.55 x Cost Index</v>
+        <v>Say ₹ 126.89 + 128.55 x Cost Index</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -1544,35 +1663,724 @@
       <c r="E51" s="2"/>
       <c r="F51" s="3"/>
     </row>
+    <row r="52" spans="1:6" ht="12.75">
+      <c r="A52" s="4">
+        <v>0</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7"/>
+    </row>
+    <row r="53" spans="1:6" ht="12.75">
+      <c r="A53" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="12.75">
+      <c r="A54" s="8"/>
+      <c r="B54" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+    </row>
+    <row r="55" spans="1:6" ht="12.75">
+      <c r="A55" s="10"/>
+      <c r="B55" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+    </row>
+    <row r="56" spans="1:6" ht="12.75">
+      <c r="A56" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="11">
+        <v>11.50</v>
+      </c>
+      <c r="E56" s="11">
+        <f t="array" ref="E56">IFERROR(INDEX(LMRRates,MATCH(A56,LMRCodes,0),),)</f>
+        <v>118</v>
+      </c>
+      <c r="F56" s="12">
+        <f>D56*E56</f>
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="12.75">
+      <c r="A57" s="10"/>
+      <c r="B57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+    </row>
+    <row r="58" spans="1:6" ht="12.75">
+      <c r="A58" s="13"/>
+      <c r="B58" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="15">
+        <f>F56*0.01</f>
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="12.75">
+      <c r="A59" s="13"/>
+      <c r="B59" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="15">
+        <f>SUM(F56:F58)</f>
+        <v>1370.57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="12.75">
+      <c r="A60" s="13"/>
+      <c r="B60" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="15">
+        <f>F59*0.15</f>
+        <v>205.5855</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="12.75">
+      <c r="A61" s="13"/>
+      <c r="B61" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="15">
+        <f>SUM(F59:F60)</f>
+        <v>1576.1555000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="12.75">
+      <c r="A62" s="13"/>
+      <c r="B62" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="15">
+        <f>F61</f>
+        <v>1576.1555000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="12.75">
+      <c r="A63" s="13"/>
+      <c r="B63" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="16">
+        <f>ROUND(F62/10,2)</f>
+        <v>157.62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="12.75">
+      <c r="A64" s="13">
+        <v>116</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="13">
+        <v>0.12</v>
+      </c>
+      <c r="E64" s="13">
+        <v>784</v>
+      </c>
+      <c r="F64" s="15">
+        <f>D64*E64</f>
+        <v>94.08</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="12.75">
+      <c r="A65" s="11">
+        <v>114</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E65" s="11">
+        <v>645</v>
+      </c>
+      <c r="F65" s="17">
+        <f>D65*E65</f>
+        <v>161.25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="12.75">
+      <c r="A66" s="10"/>
+      <c r="B66" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+    </row>
+    <row r="67" spans="1:6" ht="12.75">
+      <c r="A67" s="11">
+        <v>114</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="11">
+        <v>0.66</v>
+      </c>
+      <c r="E67" s="11">
+        <v>645</v>
+      </c>
+      <c r="F67" s="17">
+        <f>D67*E67</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="12.75">
+      <c r="A68" s="18">
+        <v>115</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="18">
+        <v>0.66</v>
+      </c>
+      <c r="E68" s="18">
+        <v>645</v>
+      </c>
+      <c r="F68" s="20">
+        <f>D68*E68</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="12.75">
+      <c r="A69" s="19"/>
+      <c r="B69" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="20">
+        <f>SUM(F64:F68)</f>
+        <v>1106.73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="12.75">
+      <c r="A70" s="19"/>
+      <c r="B70" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="20">
+        <f>F69*0.01</f>
+        <v>11.067299999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="12.75">
+      <c r="A71" s="19"/>
+      <c r="B71" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="20">
+        <f>SUM(F69:F70)</f>
+        <v>1117.7973</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="12.75">
+      <c r="A72" s="19"/>
+      <c r="B72" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="20">
+        <f>F71*0.15</f>
+        <v>167.66959499999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="12.75">
+      <c r="A73" s="19"/>
+      <c r="B73" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="20">
+        <f>SUM(F71:F72)</f>
+        <v>1285.466895</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="12.75">
+      <c r="A74" s="19"/>
+      <c r="B74" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="20">
+        <f>F73</f>
+        <v>1285.466895</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="12.75">
+      <c r="A75" s="19"/>
+      <c r="B75" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="16">
+        <f>ROUND(F74/10,2)</f>
+        <v>128.55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="12.75">
+      <c r="A76" s="22" t="str">
+        <f>CONCATENATE("Say ₹ ",F63," + ",F75," x Cost Index")</f>
+        <v>Say ₹ 157.62 + 128.55 x Cost Index</v>
+      </c>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="3"/>
+    </row>
+    <row r="77" spans="1:6" ht="12.75">
+      <c r="A77" s="23">
+        <v>0</v>
+      </c>
+      <c r="B77" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="7"/>
+    </row>
+    <row r="78" spans="1:6" ht="12.75">
+      <c r="A78" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B78" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E78" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="12.75">
+      <c r="A79" s="25"/>
+      <c r="B79" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
+    </row>
+    <row r="80" spans="1:6" ht="12.75">
+      <c r="A80" s="10"/>
+      <c r="B80" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+    </row>
+    <row r="81" spans="1:6" ht="12.75">
+      <c r="A81" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" s="27">
+        <v>11.50</v>
+      </c>
+      <c r="E81" s="27">
+        <f t="array" ref="E81">IFERROR(INDEX(LMRRates,MATCH(A81,LMRCodes,0),),)</f>
+        <v>123</v>
+      </c>
+      <c r="F81" s="28">
+        <f>D81*E81</f>
+        <v>1414.50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="12.75">
+      <c r="A82" s="10"/>
+      <c r="B82" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+    </row>
+    <row r="83" spans="1:6" ht="12.75">
+      <c r="A83" s="29"/>
+      <c r="B83" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="31">
+        <f>F81*0.01</f>
+        <v>14.145</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="12.75">
+      <c r="A84" s="29"/>
+      <c r="B84" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="31">
+        <f>SUM(F81:F83)</f>
+        <v>1428.645</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="12.75">
+      <c r="A85" s="29"/>
+      <c r="B85" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="31">
+        <f>F84*0.15</f>
+        <v>214.29675</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="12.75">
+      <c r="A86" s="29"/>
+      <c r="B86" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="31">
+        <f>SUM(F84:F85)</f>
+        <v>1642.94175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="12.75">
+      <c r="A87" s="29"/>
+      <c r="B87" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="31">
+        <f>F86</f>
+        <v>1642.94175</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="12.75">
+      <c r="A88" s="29"/>
+      <c r="B88" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="32">
+        <f>ROUND(F87/10,2)</f>
+        <v>164.29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="12.75">
+      <c r="A89" s="29">
+        <v>116</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D89" s="29">
+        <v>0.12</v>
+      </c>
+      <c r="E89" s="29">
+        <v>784</v>
+      </c>
+      <c r="F89" s="31">
+        <f>D89*E89</f>
+        <v>94.08</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="12.75">
+      <c r="A90" s="27">
+        <v>114</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D90" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="E90" s="27">
+        <v>645</v>
+      </c>
+      <c r="F90" s="33">
+        <f>D90*E90</f>
+        <v>161.25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="12.75">
+      <c r="A91" s="10"/>
+      <c r="B91" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" s="10"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="10"/>
+    </row>
+    <row r="92" spans="1:6" ht="12.75">
+      <c r="A92" s="27">
+        <v>114</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" s="27">
+        <v>0.66</v>
+      </c>
+      <c r="E92" s="27">
+        <v>645</v>
+      </c>
+      <c r="F92" s="33">
+        <f>D92*E92</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="12.75">
+      <c r="A93" s="34">
+        <v>115</v>
+      </c>
+      <c r="B93" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D93" s="34">
+        <v>0.66</v>
+      </c>
+      <c r="E93" s="34">
+        <v>645</v>
+      </c>
+      <c r="F93" s="36">
+        <f>D93*E93</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="12.75">
+      <c r="A94" s="35"/>
+      <c r="B94" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="36">
+        <f>SUM(F89:F93)</f>
+        <v>1106.73</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="12.75">
+      <c r="A95" s="35"/>
+      <c r="B95" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="36">
+        <f>F94*0.01</f>
+        <v>11.067299999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="12.75">
+      <c r="A96" s="35"/>
+      <c r="B96" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="36">
+        <f>SUM(F94:F95)</f>
+        <v>1117.7973</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="12.75">
+      <c r="A97" s="35"/>
+      <c r="B97" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="36">
+        <f>F96*0.15</f>
+        <v>167.66959499999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="12.75">
+      <c r="A98" s="35"/>
+      <c r="B98" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="36">
+        <f>SUM(F96:F97)</f>
+        <v>1285.466895</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="12.75">
+      <c r="A99" s="35"/>
+      <c r="B99" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="36">
+        <f>F98</f>
+        <v>1285.466895</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="12.75">
+      <c r="A100" s="35"/>
+      <c r="B100" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="32">
+        <f>ROUND(F99/10,2)</f>
+        <v>128.55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="12.75">
+      <c r="A101" s="38" t="str">
+        <f>CONCATENATE("Say ₹ ",F88," + ",F100," x Cost Index")</f>
+        <v>Say ₹ 164.29 + 128.55 x Cost Index</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
+  <mergeCells count="121">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
@@ -1607,6 +2415,93 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="D31:D32"/>
     <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Side Bar Files/GWD Data/PVC With Trench.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench.xlsx
@@ -933,7 +933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0507F162-605C-461B-9B56-E333CA44BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F9212B-48E9-410B-A32E-4C1ACC2DBAA6}">
   <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC With Trench.xlsx
+++ b/Side Bar Files/GWD Data/PVC With Trench.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -578,10 +578,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -933,7 +933,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F9212B-48E9-410B-A32E-4C1ACC2DBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D5D341-BFA1-4213-B566-C95D4FADBAA6}">
   <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
